--- a/data/trans_bre/IP18_E_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP18_E_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 16,89</t>
+          <t>-4,87; 15,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 3,05</t>
+          <t>-9,84; 3,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 3,49</t>
+          <t>-16,36; 2,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-33,04; 8,49</t>
+          <t>-31,84; 8,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 22,05</t>
+          <t>-5,25; 19,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 3,15</t>
+          <t>-10,17; 3,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 4,0</t>
+          <t>-17,66; 2,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 9,95</t>
+          <t>-32,71; 9,92</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 13,22</t>
+          <t>1,94; 13,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 6,87</t>
+          <t>-4,6; 7,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 1,63</t>
+          <t>-5,22; 1,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,85; 0,0</t>
+          <t>-28,04; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 15,68</t>
+          <t>2,16; 15,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 7,77</t>
+          <t>-4,84; 8,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 1,62</t>
+          <t>-5,27; 1,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,85; 0,0</t>
+          <t>-28,04; 0,0</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 3,69</t>
+          <t>-8,86; 4,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 5,09</t>
+          <t>-8,16; 4,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 10,85</t>
+          <t>-4,75; 10,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-44,26; -9,21</t>
+          <t>-42,86; -8,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 3,85</t>
+          <t>-8,97; 4,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 5,7</t>
+          <t>-8,37; 4,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 12,77</t>
+          <t>-4,99; 12,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-44,26; -9,21</t>
+          <t>-42,86; -8,52</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 7,87</t>
+          <t>-6,69; 7,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 3,58</t>
+          <t>-4,03; 3,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 10,46</t>
+          <t>-1,43; 11,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,18; 3,99</t>
+          <t>-22,37; 3,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 9,27</t>
+          <t>-7,11; 8,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 3,77</t>
+          <t>-4,05; 3,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 12,24</t>
+          <t>-1,43; 13,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,81; 4,07</t>
+          <t>-22,95; 4,17</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 4,48</t>
+          <t>-12,02; 4,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 8,98</t>
+          <t>-5,9; 9,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 1,41</t>
+          <t>-12,1; 1,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-41,17; 33,01</t>
+          <t>-36,03; 39,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 4,72</t>
+          <t>-12,08; 4,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 10,08</t>
+          <t>-6,06; 10,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 1,44</t>
+          <t>-12,66; 1,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-44,98; 52,25</t>
+          <t>-42,06; 70,6</t>
         </is>
       </c>
     </row>
@@ -1160,17 +1160,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 5,98</t>
+          <t>-9,84; 6,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 6,29</t>
+          <t>-6,32; 7,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 10,24</t>
+          <t>-2,54; 10,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 6,63</t>
+          <t>-10,31; 6,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 6,85</t>
+          <t>-6,46; 7,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 11,48</t>
+          <t>-2,57; 11,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 3,69</t>
+          <t>-7,58; 4,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 2,12</t>
+          <t>-7,42; 2,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 1,79</t>
+          <t>-6,12; 2,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-48,56; 7,37</t>
+          <t>-45,92; 4,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 4,12</t>
+          <t>-7,99; 4,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 2,31</t>
+          <t>-7,84; 2,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 1,87</t>
+          <t>-6,36; 2,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-55,24; 8,45</t>
+          <t>-52,07; 5,55</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 2,87</t>
+          <t>-4,84; 2,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 7,12</t>
+          <t>-0,85; 7,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 5,81</t>
+          <t>-3,82; 5,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,31; 8,75</t>
+          <t>-22,04; 8,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 3,03</t>
+          <t>-4,93; 3,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 7,93</t>
+          <t>-0,91; 7,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 6,5</t>
+          <t>-4,08; 6,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,79; 9,58</t>
+          <t>-22,66; 9,8</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,9</t>
+          <t>-1,85; 2,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,88</t>
+          <t>-2,03; 2,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,1</t>
+          <t>-2,12; 1,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-20,36; -3,42</t>
+          <t>-20,47; -2,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 3,21</t>
+          <t>-1,96; 3,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 2,01</t>
+          <t>-2,12; 2,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 2,25</t>
+          <t>-2,22; 2,13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-21,78; -3,7</t>
+          <t>-21,14; -3,23</t>
         </is>
       </c>
     </row>
